--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488165_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488165_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0894</v>
+        <v>3.0658</v>
       </c>
       <c r="E2" t="n">
-        <v>1.204</v>
+        <v>0.3773</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8854</v>
+        <v>2.6884</v>
       </c>
       <c r="G2" t="n">
         <v>0.9623</v>
@@ -610,13 +610,13 @@
         <v>2.0382</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7004</v>
+        <v>0.6768</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1801</v>
+        <v>0.3535</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5203</v>
+        <v>0.3233</v>
       </c>
       <c r="V2" t="n">
         <v>0.315</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ GARCIA</t>
+          <t>G. PEREZ CABRERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8083</v>
+        <v>1.4475</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3875</v>
+        <v>-0.7783</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4208</v>
+        <v>2.2258</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6506</v>
+        <v>-1.0012</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2774</v>
+        <v>-0.1578</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3732</v>
+        <v>-0.8434</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0629</v>
+        <v>-1.42</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0215</v>
+        <v>-0.1463</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0415</v>
+        <v>-1.2737</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7136</v>
+        <v>0.4188</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2989</v>
+        <v>-0.0115</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4147</v>
+        <v>0.4303</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9264</v>
+        <v>2.7793</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5325</v>
+        <v>-1.0129</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3246</v>
+        <v>-0.355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2079</v>
+        <v>-0.6579</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.4616</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.776</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. PEREZ CABRERA</t>
+          <t>D. RODRIGUEZ GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3566</v>
+        <v>0.4707</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4753</v>
+        <v>0.1484</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8318</v>
+        <v>0.3223</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0012</v>
+        <v>-0.6506</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1578</v>
+        <v>-0.2774</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8434</v>
+        <v>-0.3732</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.42</v>
+        <v>0.0629</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1463</v>
+        <v>0.0215</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2737</v>
+        <v>0.0415</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4188</v>
+        <v>-0.7136</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0115</v>
+        <v>-0.2989</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4303</v>
+        <v>-0.4147</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7793</v>
+        <v>0.9264</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.1038</v>
+        <v>0.1949</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.052</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0518</v>
+        <v>0.1094</v>
       </c>
       <c r="V5" t="n">
-        <v>3.4616</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.776</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2151</v>
+        <v>-0.1996</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9705</v>
+        <v>-1.656</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1856</v>
+        <v>1.4564</v>
       </c>
       <c r="G6" t="n">
         <v>1.3564</v>
@@ -922,13 +922,13 @@
         <v>0.7411</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1557</v>
+        <v>-0.259</v>
       </c>
       <c r="T6" t="n">
-        <v>0.965</v>
+        <v>0.2795</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8093</v>
+        <v>-0.5385</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. FROUFE PEREZ</t>
+          <t>S. VICENTE GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0829</v>
+        <v>-0.2264</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.7718</v>
+        <v>-1.5439</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6888</v>
+        <v>1.3176</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0847</v>
+        <v>-2.1426</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9819</v>
+        <v>-1.5726</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8972</v>
+        <v>-0.5699</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4416</v>
+        <v>-1.177</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8629</v>
+        <v>-0.5455</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3045</v>
+        <v>-0.6315</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5263</v>
+        <v>-0.9656</v>
       </c>
       <c r="N7" t="n">
-        <v>0.119</v>
+        <v>-1.0271</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4073</v>
+        <v>0.0616</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7411</v>
+        <v>0.7411</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.7793</v>
+        <v>-1.1117</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5735</v>
+        <v>0.5456</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1803</v>
+        <v>0.1154</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7538</v>
+        <v>0.4303</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="W7" t="n">
         <v>0.6294</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. VICENTE GARCIA</t>
+          <t>A. FROUFE PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8008</v>
+        <v>-0.5212</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.143</v>
+        <v>-2.6191</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3422</v>
+        <v>2.0979</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1426</v>
+        <v>0.0847</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5726</v>
+        <v>0.9819</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5699</v>
+        <v>-0.8972</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.177</v>
+        <v>-0.4416</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5455</v>
+        <v>0.8629</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6315</v>
+        <v>-1.3045</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9656</v>
+        <v>0.5263</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0271</v>
+        <v>0.119</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0616</v>
+        <v>0.4073</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7411</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1117</v>
+        <v>-2.7793</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8529</v>
+        <v>2.0382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0288</v>
+        <v>0.1352</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4837</v>
+        <v>-0.0276</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4549</v>
+        <v>0.1629</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0.6294</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MALICK</t>
+          <t>J. QUINTA RAMOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1943</v>
+        <v>-2.2061</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.2371</v>
+        <v>-2.8662</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0427</v>
+        <v>0.6601</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5336</v>
+        <v>1.0672</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.357</v>
+        <v>0.5954</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1766</v>
+        <v>0.4718</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.6448</v>
+        <v>0.5266</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1684</v>
+        <v>0.4851</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.4763</v>
+        <v>0.0415</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1112</v>
+        <v>0.5406</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1885</v>
+        <v>0.1103</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2997</v>
+        <v>0.4303</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.4087</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.7439</v>
+        <v>-2.9646</v>
       </c>
       <c r="R9" t="n">
-        <v>3.3352</v>
+        <v>1.1117</v>
       </c>
       <c r="S9" t="n">
-        <v>2.118</v>
+        <v>-0.476</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9489</v>
+        <v>0.2018</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1691</v>
+        <v>-0.6778</v>
       </c>
       <c r="V9" t="n">
-        <v>0.63</v>
+        <v>-0.9444</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2027</v>
+        <v>-0.63</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5727</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. QUINTA RAMOS</t>
+          <t>M. MALICK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3156</v>
+        <v>-2.7529</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6064</v>
+        <v>-5.5741</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2908</v>
+        <v>2.8212</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0672</v>
+        <v>-2.5336</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5954</v>
+        <v>-0.357</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4718</v>
+        <v>-2.1766</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5266</v>
+        <v>-2.6448</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4851</v>
+        <v>-0.1684</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0415</v>
+        <v>-2.4763</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5406</v>
+        <v>0.1112</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1103</v>
+        <v>-0.1885</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4303</v>
+        <v>0.2997</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8529</v>
+        <v>-2.4087</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9646</v>
+        <v>-5.7439</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1117</v>
+        <v>3.3352</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5855</v>
+        <v>1.5594</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5384</v>
+        <v>0.6119</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0471</v>
+        <v>0.9475</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9444</v>
+        <v>0.63</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.63</v>
+        <v>2.2027</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3144</v>
+        <v>-1.5727</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4612</v>
+        <v>-3.9163</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.6944</v>
+        <v>-6.2479</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2331</v>
+        <v>2.3316</v>
       </c>
       <c r="G11" t="n">
         <v>-3.2176</v>
@@ -1312,13 +1312,13 @@
         <v>2.7793</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2174</v>
+        <v>0.7623</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3991</v>
+        <v>0.0473</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6165</v>
+        <v>0.715</v>
       </c>
       <c r="V11" t="n">
         <v>-2.2022</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.763299999999999</v>
+        <v>-4.2164</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.6849</v>
+        <v>-20.1377</v>
       </c>
       <c r="F12" t="n">
-        <v>15.9212</v>
+        <v>15.9213</v>
       </c>
       <c r="G12" t="n">
         <v>-5.4529</v>
@@ -1390,13 +1390,13 @@
         <v>17.6023</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5794</v>
+        <v>2.1263</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7650999999999997</v>
+        <v>1.3123</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8143000000000002</v>
+        <v>0.8142</v>
       </c>
       <c r="V12" t="n">
         <v>1.8894</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.4918</v>
+        <v>6.4891</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9709</v>
+        <v>2.0688</v>
       </c>
       <c r="F13" t="n">
-        <v>4.5209</v>
+        <v>4.4202</v>
       </c>
       <c r="G13" t="n">
         <v>3.5907</v>
@@ -1468,13 +1468,13 @@
         <v>3.1499</v>
       </c>
       <c r="S13" t="n">
-        <v>0.863</v>
+        <v>0.8602</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0199</v>
+        <v>0.0781</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8829</v>
+        <v>0.7822</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. FAJANA</t>
+          <t>M. GARCIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0002</v>
+        <v>2.712</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.4798</v>
+        <v>1.2468</v>
       </c>
       <c r="F14" t="n">
-        <v>4.48</v>
+        <v>1.4652</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1246</v>
+        <v>0.9769</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4026</v>
+        <v>0.347</v>
       </c>
       <c r="I14" t="n">
-        <v>0.278</v>
+        <v>0.6299</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.3641</v>
+        <v>0.0772</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.7741</v>
+        <v>0.0772</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.59</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2395</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3715</v>
+        <v>0.2699</v>
       </c>
       <c r="O14" t="n">
-        <v>0.868</v>
+        <v>0.6299</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8529</v>
+        <v>0.9264</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1429</v>
+        <v>-0.3243</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0707</v>
+        <v>-0.0892</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0721</v>
+        <v>-0.235</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3144</v>
+        <v>1.133</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.0011</v>
+        <v>1.2589</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3155</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GARCIA FERNANDEZ</t>
+          <t>O. FAJANA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9848</v>
+        <v>2.206</v>
       </c>
       <c r="E15" t="n">
-        <v>0.953</v>
+        <v>-2.0673</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0317</v>
+        <v>4.2733</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9769</v>
+        <v>-1.1246</v>
       </c>
       <c r="H15" t="n">
-        <v>0.347</v>
+        <v>-1.4026</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6299</v>
+        <v>0.278</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0772</v>
+        <v>-2.3641</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0772</v>
+        <v>-1.7741</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.59</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8997000000000001</v>
+        <v>1.2395</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2699</v>
+        <v>0.3715</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6299</v>
+        <v>0.868</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9264</v>
+        <v>1.8529</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0515</v>
+        <v>1.3486</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.383</v>
+        <v>0.4831</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6685</v>
+        <v>0.8655</v>
       </c>
       <c r="V15" t="n">
-        <v>1.133</v>
+        <v>0.3144</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2589</v>
+        <v>-0.0011</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1259</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. DELGADO YEBOAH</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8384</v>
+        <v>1.8718</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.5231</v>
+        <v>0.2776</v>
       </c>
       <c r="F16" t="n">
-        <v>4.3615</v>
+        <v>1.5942</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2378</v>
+        <v>2.6169</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0998</v>
+        <v>2.0392</v>
       </c>
       <c r="I16" t="n">
-        <v>0.138</v>
+        <v>0.5777</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3644</v>
+        <v>1.8851</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1121</v>
+        <v>1.7606</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2523</v>
+        <v>0.1244</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6022</v>
+        <v>0.7319</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2119</v>
+        <v>0.2786</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3903</v>
+        <v>0.4533</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3706</v>
+        <v>1.297</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9646</v>
+        <v>-1.297</v>
       </c>
       <c r="R16" t="n">
-        <v>3.3352</v>
+        <v>2.594</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7265</v>
+        <v>-0.9718</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1764</v>
+        <v>-0.6249</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4499</v>
+        <v>-0.347</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5034999999999999</v>
+        <v>-1.0703</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6294</v>
+        <v>0.3144</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1259</v>
+        <v>-1.3847</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>K. DELGADO YEBOAH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1932</v>
+        <v>1.3986</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0818</v>
+        <v>-3.5024</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1115</v>
+        <v>4.901</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6169</v>
+        <v>0.2378</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0392</v>
+        <v>0.0998</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5777</v>
+        <v>0.138</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8851</v>
+        <v>-1.3644</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7606</v>
+        <v>-0.1121</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1244</v>
+        <v>-1.2523</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7319</v>
+        <v>1.6022</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2786</v>
+        <v>0.2119</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4533</v>
+        <v>1.3903</v>
       </c>
       <c r="P17" t="n">
-        <v>1.297</v>
+        <v>0.3706</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.297</v>
+        <v>-2.9646</v>
       </c>
       <c r="R17" t="n">
-        <v>2.594</v>
+        <v>3.3352</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6504</v>
+        <v>0.2866</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8207</v>
+        <v>0.1971</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8297</v>
+        <v>0.0895</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0703</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3144</v>
+        <v>0.6294</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3847</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GALLEGO GÓMEZ</t>
+          <t>S. TRUJILLO SUAREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6221</v>
+        <v>0.889</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6221</v>
+        <v>-0.8912</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.7801</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6221</v>
+        <v>-0.052</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.0766</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6221</v>
+        <v>0.0246</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6221</v>
+        <v>-0.3922</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.1671</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6221</v>
+        <v>-0.5592</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.3402</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.2437</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.5839</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.297</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.0382</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.5148</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.1691</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.3457</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. TRUJILLO SUAREZ</t>
+          <t>A. GALLEGO GÓMEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2287</v>
+        <v>0.6221</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6746</v>
+        <v>0.6221</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9033</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.052</v>
+        <v>0.6221</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0766</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0246</v>
+        <v>0.6221</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3922</v>
+        <v>0.6221</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1671</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5592</v>
+        <v>0.6221</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3402</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2437</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5839</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.297</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1455</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6143</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4688</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.239</v>
+        <v>0.2105</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0582</v>
+        <v>0.2541</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2972</v>
+        <v>-0.0435</v>
       </c>
       <c r="G20" t="n">
         <v>0.6563</v>
@@ -2014,13 +2014,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5074</v>
+        <v>-0.0578</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3283</v>
+        <v>-0.1324</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1791</v>
+        <v>0.0746</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9439</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2175</v>
+        <v>-0.7828000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4714</v>
+        <v>-2.6673</v>
       </c>
       <c r="F21" t="n">
-        <v>1.254</v>
+        <v>1.8845</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8731</v>
@@ -2092,13 +2092,13 @@
         <v>2.7793</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1405</v>
+        <v>0.2941</v>
       </c>
       <c r="T21" t="n">
-        <v>0.199</v>
+        <v>0.0031</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3395</v>
+        <v>0.291</v>
       </c>
       <c r="V21" t="n">
         <v>-0.945</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3294</v>
+        <v>-3.8643</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.5541</v>
+        <v>-5.4562</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2247</v>
+        <v>1.5918</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8286</v>
@@ -2170,13 +2170,13 @@
         <v>2.2234</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.061</v>
+        <v>-0.596</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8754</v>
+        <v>-0.7775</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1856</v>
+        <v>0.1815</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6986</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8099</v>
+        <v>-4.377</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.9043</v>
+        <v>-5.8064</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0944</v>
+        <v>1.4294</v>
       </c>
       <c r="G23" t="n">
         <v>-0.3695</v>
@@ -2248,13 +2248,13 @@
         <v>0.9264</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7553</v>
+        <v>-0.3224</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2189</v>
+        <v>-0.1209</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5365</v>
+        <v>-0.2015</v>
       </c>
       <c r="V23" t="n">
         <v>1.1324</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.7634</v>
+        <v>7.375000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-15.9213</v>
+        <v>-15.9214</v>
       </c>
       <c r="F24" t="n">
-        <v>20.6848</v>
+        <v>23.2962</v>
       </c>
       <c r="G24" t="n">
-        <v>5.4529</v>
+        <v>5.452899999999999</v>
       </c>
       <c r="H24" t="n">
         <v>2.6114</v>
@@ -2326,13 +2326,13 @@
         <v>20.3816</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5792</v>
+        <v>1.032</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8143999999999999</v>
+        <v>-0.8144</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.765</v>
+        <v>1.8465</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8895</v>
